--- a/ボランティア楽校_開催準備リスト_20261215.xlsx
+++ b/ボランティア楽校_開催準備リスト_20261215.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'当日の流れ'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'準備リスト'!$A$4:$K$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'準備リスト'!$A$4:$K$120</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'準備リスト'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'逆算スケジュール'!$4:$4</definedName>
   </definedNames>
@@ -1331,7 +1331,7 @@
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>・「準備リスト」… やることを115項目、締切の早い順にならべています。</t>
+          <t>・「準備リスト」… やることを116項目、締切の早い順にならべています。</t>
         </is>
       </c>
       <c r="B14" s="11" t="n"/>
@@ -2126,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K119"/>
+  <dimension ref="A1:K120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2985,12 +2985,12 @@
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>盆栽を当日どこに入れるか決める</t>
+          <t>盆栽コーナーの見せ方を決める</t>
         </is>
       </c>
       <c r="G21" s="26" t="inlineStr">
         <is>
-          <t>自由見学（11:00〜12:00）のコーナーに置くのが自然。作業に30分以上かかる内容なら、別の日に回す判断も</t>
+          <t>紹介がメインで、体験は希望者のみ。活動のようすが分かる展示と、体験用の席を数席、という形に</t>
         </is>
       </c>
       <c r="H21" s="27" t="n"/>
@@ -6248,17 +6248,17 @@
       </c>
       <c r="E101" s="26" t="inlineStr">
         <is>
-          <t>I 当日の運営</t>
+          <t>G 盆栽ボランティアの準備</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>動線のリハーサルをする（30分でよい）</t>
+          <t>申込フォームから盆栽体験の希望者数を数え、材料をそろえる</t>
         </is>
       </c>
       <c r="G101" s="26" t="inlineStr">
         <is>
-          <t>入口から受付、席、盆栽コーナー、手洗い、災ボラコーナーまで、実際に歩いてみる</t>
+          <t>スクリプトの checkSetup を実行すると、体験希望者の人数が出ます。予備を2〜3セット足しておく</t>
         </is>
       </c>
       <c r="H101" s="27" t="n"/>
@@ -6275,7 +6275,7 @@
         <v>98</v>
       </c>
       <c r="B102" s="33">
-        <f>使い方!$B$5-1</f>
+        <f>使い方!$B$5-7</f>
         <v/>
       </c>
       <c r="C102" s="34">
@@ -6284,22 +6284,22 @@
       </c>
       <c r="D102" s="35" t="inlineStr">
         <is>
-          <t>前日</t>
+          <t>1週前</t>
         </is>
       </c>
       <c r="E102" s="26" t="inlineStr">
         <is>
-          <t>B 事務の手続き</t>
+          <t>I 当日の運営</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>会場使用料の支払い</t>
+          <t>動線のリハーサルをする（30分でよい）</t>
         </is>
       </c>
       <c r="G102" s="26" t="inlineStr">
         <is>
-          <t>参加費を取らないことになったため、釣り銭の準備は不要</t>
+          <t>入口から受付、席、盆栽コーナー、手洗い、災ボラコーナーまで、実際に歩いてみる</t>
         </is>
       </c>
       <c r="H102" s="27" t="n"/>
@@ -6330,17 +6330,17 @@
       </c>
       <c r="E103" s="26" t="inlineStr">
         <is>
-          <t>C チラシと広報</t>
+          <t>B 事務の手続き</t>
         </is>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>声をかけた方へリマインドの電話</t>
+          <t>会場使用料の支払い</t>
         </is>
       </c>
       <c r="G103" s="26" t="inlineStr">
         <is>
-          <t>「明日お待ちしています」の一本で、来場がはっきり変わります</t>
+          <t>参加費を取らないことになったため、釣り銭の準備は不要</t>
         </is>
       </c>
       <c r="H103" s="27" t="n"/>
@@ -6371,17 +6371,17 @@
       </c>
       <c r="E104" s="26" t="inlineStr">
         <is>
-          <t>E カフェで使う備品</t>
+          <t>C チラシと広報</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>積み込みリストで最終確認をする</t>
+          <t>声をかけた方へリマインドの電話</t>
         </is>
       </c>
       <c r="G104" s="26" t="inlineStr">
         <is>
-          <t>この欄をそのまま印刷して、チェックしながら積む</t>
+          <t>「明日お待ちしています」の一本で、来場がはっきり変わります</t>
         </is>
       </c>
       <c r="H104" s="27" t="n"/>
@@ -6412,17 +6412,17 @@
       </c>
       <c r="E105" s="26" t="inlineStr">
         <is>
-          <t>I 当日の運営</t>
+          <t>E カフェで使う備品</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>積み込み</t>
+          <t>積み込みリストで最終確認をする</t>
         </is>
       </c>
       <c r="G105" s="26" t="inlineStr">
         <is>
-          <t>Eの備品リストと、盆栽の材料、災ボラの資料一式、表示物、記念品</t>
+          <t>この欄をそのまま印刷して、チェックしながら積む</t>
         </is>
       </c>
       <c r="H105" s="27" t="n"/>
@@ -6439,7 +6439,7 @@
         <v>102</v>
       </c>
       <c r="B106" s="33">
-        <f>使い方!$B$5+0</f>
+        <f>使い方!$B$5-1</f>
         <v/>
       </c>
       <c r="C106" s="34">
@@ -6448,22 +6448,22 @@
       </c>
       <c r="D106" s="35" t="inlineStr">
         <is>
-          <t>当日</t>
+          <t>前日</t>
         </is>
       </c>
       <c r="E106" s="26" t="inlineStr">
         <is>
-          <t>G 盆栽ボランティアの準備</t>
+          <t>I 当日の運営</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>「この続きをやりたい人」の名簿をその場でつくる</t>
+          <t>積み込み</t>
         </is>
       </c>
       <c r="G106" s="26" t="inlineStr">
         <is>
-          <t>庭木・鉢の手入れを手伝う活動へ。教えてくれた方にも、世話人として関わってもらえるか声をかける</t>
+          <t>Eの備品リストと、盆栽の材料、災ボラの資料一式、表示物、記念品</t>
         </is>
       </c>
       <c r="H106" s="27" t="n"/>
@@ -6494,17 +6494,17 @@
       </c>
       <c r="E107" s="26" t="inlineStr">
         <is>
-          <t>I 当日の運営</t>
+          <t>G 盆栽ボランティアの準備</t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>開場90分前に集合。設営・掲示・給湯・受付準備</t>
+          <t>「この続きをやりたい人」の名簿をその場でつくる</t>
         </is>
       </c>
       <c r="G107" s="26" t="inlineStr">
         <is>
-          <t>机といすの数を実際に数える。90分前でも足りないことがあります</t>
+          <t>庭木・鉢の手入れを手伝う活動へ。教えてくれた方にも、世話人として関わってもらえるか声をかける</t>
         </is>
       </c>
       <c r="H107" s="27" t="n"/>
@@ -6540,12 +6540,12 @@
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>はじめての方に、世話人か職員がひとりつく</t>
+          <t>開場90分前に集合。設営・掲示・給湯・受付準備</t>
         </is>
       </c>
       <c r="G108" s="26" t="inlineStr">
         <is>
-          <t>いちばん大事な役です。担当を先に決めておく</t>
+          <t>机といすの数を実際に数える。90分前でも足りないことがあります</t>
         </is>
       </c>
       <c r="H108" s="27" t="n"/>
@@ -6581,12 +6581,12 @@
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>記録をとる</t>
+          <t>はじめての方に、世話人か職員がひとりつく</t>
         </is>
       </c>
       <c r="G109" s="26" t="inlineStr">
         <is>
-          <t>参加者数／はじめて来た人／出た話題／気になった方／つないだ先／写真</t>
+          <t>いちばん大事な役です。担当を先に決めておく</t>
         </is>
       </c>
       <c r="H109" s="27" t="n"/>
@@ -6622,10 +6622,14 @@
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>「やってみたいこと」「出られる曜日」を書いて帰ってもらう</t>
-        </is>
-      </c>
-      <c r="G110" s="26" t="n"/>
+          <t>記録をとる</t>
+        </is>
+      </c>
+      <c r="G110" s="26" t="inlineStr">
+        <is>
+          <t>参加者数／はじめて来た人／出た話題／気になった方／つないだ先／写真</t>
+        </is>
+      </c>
       <c r="H110" s="27" t="n"/>
       <c r="I110" s="27" t="inlineStr">
         <is>
@@ -6659,14 +6663,10 @@
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t>終了後15分でふりかえり。次回に変えることを1つだけ決める</t>
-        </is>
-      </c>
-      <c r="G111" s="26" t="inlineStr">
-        <is>
-          <t>その場で決めないと、次回まで持ち越されて忘れます</t>
-        </is>
-      </c>
+          <t>「やってみたいこと」「出られる曜日」を書いて帰ってもらう</t>
+        </is>
+      </c>
+      <c r="G111" s="26" t="n"/>
       <c r="H111" s="27" t="n"/>
       <c r="I111" s="27" t="inlineStr">
         <is>
@@ -6690,22 +6690,22 @@
       </c>
       <c r="D112" s="35" t="inlineStr">
         <is>
-          <t>当日中</t>
+          <t>当日</t>
         </is>
       </c>
       <c r="E112" s="26" t="inlineStr">
         <is>
-          <t>J 終わったあと</t>
+          <t>I 当日の運営</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>開催記録を書く</t>
+          <t>終了後15分でふりかえり。次回に変えることを1つだけ決める</t>
         </is>
       </c>
       <c r="G112" s="26" t="inlineStr">
         <is>
-          <t>記憶が新しいうちに。第1期以降の評価は、この記録の積み重ねでしか出せません</t>
+          <t>その場で決めないと、次回まで持ち越されて忘れます</t>
         </is>
       </c>
       <c r="H112" s="27" t="n"/>
@@ -6722,7 +6722,7 @@
         <v>109</v>
       </c>
       <c r="B113" s="33">
-        <f>使い方!$B$5+3</f>
+        <f>使い方!$B$5+0</f>
         <v/>
       </c>
       <c r="C113" s="34">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="D113" s="35" t="inlineStr">
         <is>
-          <t>3日以内</t>
+          <t>当日中</t>
         </is>
       </c>
       <c r="E113" s="26" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t>講師・協力者・会場へお礼</t>
+          <t>開催記録を書く</t>
         </is>
       </c>
       <c r="G113" s="26" t="inlineStr">
         <is>
-          <t>盆栽を教えてくれた方には、当日の写真を添えて</t>
+          <t>記憶が新しいうちに。第1期以降の評価は、この記録の積み重ねでしか出せません</t>
         </is>
       </c>
       <c r="H113" s="27" t="n"/>
@@ -6763,7 +6763,7 @@
         <v>110</v>
       </c>
       <c r="B114" s="33">
-        <f>使い方!$B$5+7</f>
+        <f>使い方!$B$5+3</f>
         <v/>
       </c>
       <c r="C114" s="34">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="D114" s="35" t="inlineStr">
         <is>
-          <t>1週以内</t>
+          <t>3日以内</t>
         </is>
       </c>
       <c r="E114" s="26" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>写真を整理し、使ってよいものを選ぶ</t>
+          <t>講師・協力者・会場へお礼</t>
         </is>
       </c>
       <c r="G114" s="26" t="inlineStr">
         <is>
-          <t>写りたくないと申し出た方が入っていないか、必ず確認する</t>
+          <t>盆栽を教えてくれた方には、当日の写真を添えて</t>
         </is>
       </c>
       <c r="H114" s="27" t="n"/>
@@ -6823,10 +6823,14 @@
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t>支出を精算する</t>
-        </is>
-      </c>
-      <c r="G115" s="26" t="n"/>
+          <t>写真を整理し、使ってよいものを選ぶ</t>
+        </is>
+      </c>
+      <c r="G115" s="26" t="inlineStr">
+        <is>
+          <t>写りたくないと申し出た方が入っていないか、必ず確認する</t>
+        </is>
+      </c>
       <c r="H115" s="27" t="n"/>
       <c r="I115" s="27" t="inlineStr">
         <is>
@@ -6860,14 +6864,10 @@
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t>参加者へ次回のお知らせ</t>
-        </is>
-      </c>
-      <c r="G116" s="26" t="inlineStr">
-        <is>
-          <t>希望された方へ。第2回の日付だけでも早く伝える</t>
-        </is>
-      </c>
+          <t>支出を精算する</t>
+        </is>
+      </c>
+      <c r="G116" s="26" t="n"/>
       <c r="H116" s="27" t="n"/>
       <c r="I116" s="27" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>113</v>
       </c>
       <c r="B117" s="33">
-        <f>使い方!$B$5+14</f>
+        <f>使い方!$B$5+7</f>
         <v/>
       </c>
       <c r="C117" s="34">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="D117" s="35" t="inlineStr">
         <is>
-          <t>2週以内</t>
+          <t>1週以内</t>
         </is>
       </c>
       <c r="E117" s="26" t="inlineStr">
@@ -6901,12 +6901,12 @@
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
-          <t>運営委員会・事務局へ報告する</t>
+          <t>参加者へ次回のお知らせ</t>
         </is>
       </c>
       <c r="G117" s="26" t="inlineStr">
         <is>
-          <t>人数だけでなく、その日に生まれた会話や関係も書く</t>
+          <t>希望された方へ。第2回の日付だけでも早く伝える</t>
         </is>
       </c>
       <c r="H117" s="27" t="n"/>
@@ -6916,11 +6916,7 @@
         </is>
       </c>
       <c r="J117" s="36" t="n"/>
-      <c r="K117" s="37" t="inlineStr">
-        <is>
-          <t>12月29日は年末休みの可能性。12月28日までに</t>
-        </is>
-      </c>
+      <c r="K117" s="37" t="n"/>
     </row>
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="32" t="n">
@@ -6946,12 +6942,12 @@
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t>参加者カードを整理し、保管する</t>
+          <t>運営委員会・事務局へ報告する</t>
         </is>
       </c>
       <c r="G118" s="26" t="inlineStr">
         <is>
-          <t>次回「カフェ以外で会いましたか」を聞くための土台になります</t>
+          <t>人数だけでなく、その日に生まれた会話や関係も書く</t>
         </is>
       </c>
       <c r="H118" s="27" t="n"/>
@@ -6991,12 +6987,12 @@
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t>盆栽の続きを希望した方へ連絡する</t>
+          <t>参加者カードを整理し、保管する</t>
         </is>
       </c>
       <c r="G119" s="26" t="inlineStr">
         <is>
-          <t>熱があるうちに。2週間空くと、気持ちは戻ってしまいます</t>
+          <t>次回「カフェ以外で会いましたか」を聞くための土台になります</t>
         </is>
       </c>
       <c r="H119" s="27" t="n"/>
@@ -7012,9 +7008,54 @@
         </is>
       </c>
     </row>
+    <row r="120" ht="30" customHeight="1">
+      <c r="A120" s="32" t="n">
+        <v>116</v>
+      </c>
+      <c r="B120" s="33">
+        <f>使い方!$B$5+14</f>
+        <v/>
+      </c>
+      <c r="C120" s="34">
+        <f>CHOOSE(WEEKDAY(B120),"日","月","火","水","木","金","土")</f>
+        <v/>
+      </c>
+      <c r="D120" s="35" t="inlineStr">
+        <is>
+          <t>2週以内</t>
+        </is>
+      </c>
+      <c r="E120" s="26" t="inlineStr">
+        <is>
+          <t>J 終わったあと</t>
+        </is>
+      </c>
+      <c r="F120" s="10" t="inlineStr">
+        <is>
+          <t>盆栽の続きを希望した方へ連絡する</t>
+        </is>
+      </c>
+      <c r="G120" s="26" t="inlineStr">
+        <is>
+          <t>熱があるうちに。2週間空くと、気持ちは戻ってしまいます</t>
+        </is>
+      </c>
+      <c r="H120" s="27" t="n"/>
+      <c r="I120" s="27" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J120" s="36" t="n"/>
+      <c r="K120" s="37" t="inlineStr">
+        <is>
+          <t>12月29日は年末休みの可能性。12月28日までに</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:K119"/>
-  <conditionalFormatting sqref="A5:K119">
+  <autoFilter ref="A4:K120"/>
+  <conditionalFormatting sqref="A5:K120">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>AND($B5&lt;TODAY(),$I5&lt;&gt;"完了",$I5&lt;&gt;"対象外")</formula>
     </cfRule>
@@ -7023,7 +7064,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="I5:I119" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="状況" prompt="選んでください" type="list">
+    <dataValidation sqref="I5:I120" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="状況" prompt="選んでください" type="list">
       <formula1>"未着手,準備中,完了,対象外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7127,11 +7168,11 @@
         </is>
       </c>
       <c r="E5" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$C5)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$C5)</f>
         <v/>
       </c>
       <c r="F5" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C5,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$C5,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="G5" s="41">
@@ -7164,11 +7205,11 @@
         </is>
       </c>
       <c r="E6" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$C6)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$C6)</f>
         <v/>
       </c>
       <c r="F6" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C6,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$C6,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="G6" s="41">
@@ -7201,11 +7242,11 @@
         </is>
       </c>
       <c r="E7" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$C7)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$C7)</f>
         <v/>
       </c>
       <c r="F7" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C7,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$C7,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="G7" s="41">
@@ -7238,11 +7279,11 @@
         </is>
       </c>
       <c r="E8" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$C8)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$C8)</f>
         <v/>
       </c>
       <c r="F8" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C8,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$C8,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="G8" s="41">
@@ -7271,11 +7312,11 @@
         </is>
       </c>
       <c r="E9" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$C9)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$C9)</f>
         <v/>
       </c>
       <c r="F9" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C9,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$C9,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="G9" s="41">
@@ -7308,11 +7349,11 @@
         </is>
       </c>
       <c r="E10" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$C10)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$C10)</f>
         <v/>
       </c>
       <c r="F10" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C10,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$C10,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="G10" s="41">
@@ -7345,11 +7386,11 @@
         </is>
       </c>
       <c r="E11" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$C11)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$C11)</f>
         <v/>
       </c>
       <c r="F11" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C11,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$C11,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="G11" s="41">
@@ -7382,11 +7423,11 @@
         </is>
       </c>
       <c r="E12" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$C12)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$C12)</f>
         <v/>
       </c>
       <c r="F12" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C12,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$C12,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="G12" s="41">
@@ -7419,11 +7460,11 @@
         </is>
       </c>
       <c r="E13" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$C13)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$C13)</f>
         <v/>
       </c>
       <c r="F13" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C13,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$C13,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="G13" s="41">
@@ -7456,11 +7497,11 @@
         </is>
       </c>
       <c r="E14" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$C14)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$C14)</f>
         <v/>
       </c>
       <c r="F14" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C14,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$C14,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="G14" s="41">
@@ -7489,11 +7530,11 @@
         </is>
       </c>
       <c r="E15" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$C15)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$C15)</f>
         <v/>
       </c>
       <c r="F15" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C15,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$C15,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="G15" s="41">
@@ -7526,11 +7567,11 @@
         </is>
       </c>
       <c r="E16" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$C16)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$C16)</f>
         <v/>
       </c>
       <c r="F16" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C16,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$C16,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="G16" s="41">
@@ -7563,11 +7604,11 @@
         </is>
       </c>
       <c r="E17" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$C17)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$C17)</f>
         <v/>
       </c>
       <c r="F17" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C17,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$C17,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="G17" s="41">
@@ -7600,11 +7641,11 @@
         </is>
       </c>
       <c r="E18" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$C18)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$C18)</f>
         <v/>
       </c>
       <c r="F18" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C18,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$C18,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="G18" s="41">
@@ -7637,11 +7678,11 @@
         </is>
       </c>
       <c r="E19" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$C19)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$C19)</f>
         <v/>
       </c>
       <c r="F19" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C19,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$C19,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="G19" s="41">
@@ -7674,11 +7715,11 @@
         </is>
       </c>
       <c r="E20" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$C20)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$C20)</f>
         <v/>
       </c>
       <c r="F20" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C20,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$C20,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="G20" s="41">
@@ -7936,14 +7977,14 @@
       </c>
       <c r="B12" s="26" t="inlineStr">
         <is>
-          <t>苗・鉢・用土・鉢底ネット・化粧砂。1人1セット</t>
+          <t>苗・鉢・用土・鉢底ネット・化粧砂。体験を希望した方の分だけ</t>
         </is>
       </c>
       <c r="C12" s="49" t="n">
         <v>700</v>
       </c>
       <c r="D12" s="49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E12" s="50">
         <f>C12*D12</f>
@@ -7951,7 +7992,7 @@
       </c>
       <c r="F12" s="51" t="inlineStr">
         <is>
-          <t>希望者15人分。参加者全員分は予算に入りません</t>
+          <t>紹介がメインで、体験は希望者のみ。申込フォームの希望者数に合わせて数量を直してください</t>
         </is>
       </c>
     </row>
@@ -8069,7 +8110,7 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="28" t="inlineStr">
         <is>
-          <t>※ 単価・数量はすべて、この表をつくった時点での仮置きです。実際の見積に置き換えてください。総額50,000円は9/2時点で示された額です。参加費は取らないことになったため（9/4）、収入はありません。チラシで定員が50人になったため、茶菓と記念品を55人分で組み直し、単価を下げました。段ボールベッドは町の備蓄から借りる想定で数量0にしています。不足分を買う場合は1台あたり約3,000円かかり、その分は記念品の単価か、盆栽の材料の数を減らして捻出することになります。防災バッグは役場総務課防災対策室からの借用のため、費用は見込んでいません。盆栽の材料は希望者15人分で組んでいます。盆栽の道具（はさみ・じょうろ・シート等）は手持ちや借用でまかなうため、予算には計上していません（9/15のご指示）。合計と残りは下の行に自動で出ます。残りがマイナスになったら、どこかを削ってください。</t>
+          <t>※ 単価・数量はすべて、この表をつくった時点での仮置きです。実際の見積に置き換えてください。総額50,000円は9/2時点で示された額です。参加費は取らないことになったため（9/4）、収入はありません。チラシで定員が50人になったため、茶菓と記念品を55人分で組み直し、単価を下げました。段ボールベッドは町の備蓄から借りる想定で数量0にしています。不足分を買う場合は1台あたり約3,000円かかり、その分は記念品の単価か、盆栽の材料の数を減らして捻出することになります。防災バッグは役場総務課防災対策室からの借用のため、費用は見込んでいません。盆栽は紹介がメインで、体験は希望者のみです。材料はひとまず10人分で置いていますが、申込フォームの「盆栽づくりを体験してみたい」の人数が分かりしだい直してください（1セット700円）。盆栽の道具（はさみ・じょうろ・シート等）は手持ちや借用でまかなうため、予算には計上していません（9/15のご指示）。合計と残りは下の行に自動で出ます。残りがマイナスになったら、どこかを削ってください。</t>
         </is>
       </c>
     </row>
@@ -8172,11 +8213,11 @@
         </is>
       </c>
       <c r="B5" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A5,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$A5,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="C5" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$A5)-B5</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$A5)-B5</f>
         <v/>
       </c>
       <c r="D5" s="57">
@@ -8189,11 +8230,11 @@
         </is>
       </c>
       <c r="G5" s="40">
-        <f>COUNTIFS(準備リスト!$E$5:$E$119,$F5,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$E$5:$E$120,$F5,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="H5" s="40">
-        <f>COUNTIF(準備リスト!$E$5:$E$119,$F5)-G5</f>
+        <f>COUNTIF(準備リスト!$E$5:$E$120,$F5)-G5</f>
         <v/>
       </c>
       <c r="I5" s="57">
@@ -8208,11 +8249,11 @@
         </is>
       </c>
       <c r="B6" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A6,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$A6,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="C6" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$A6)-B6</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$A6)-B6</f>
         <v/>
       </c>
       <c r="D6" s="57">
@@ -8225,11 +8266,11 @@
         </is>
       </c>
       <c r="G6" s="40">
-        <f>COUNTIFS(準備リスト!$E$5:$E$119,$F6,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$E$5:$E$120,$F6,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="H6" s="40">
-        <f>COUNTIF(準備リスト!$E$5:$E$119,$F6)-G6</f>
+        <f>COUNTIF(準備リスト!$E$5:$E$120,$F6)-G6</f>
         <v/>
       </c>
       <c r="I6" s="57">
@@ -8244,11 +8285,11 @@
         </is>
       </c>
       <c r="B7" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A7,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$A7,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="C7" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$A7)-B7</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$A7)-B7</f>
         <v/>
       </c>
       <c r="D7" s="57">
@@ -8261,11 +8302,11 @@
         </is>
       </c>
       <c r="G7" s="40">
-        <f>COUNTIFS(準備リスト!$E$5:$E$119,$F7,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$E$5:$E$120,$F7,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="H7" s="40">
-        <f>COUNTIF(準備リスト!$E$5:$E$119,$F7)-G7</f>
+        <f>COUNTIF(準備リスト!$E$5:$E$120,$F7)-G7</f>
         <v/>
       </c>
       <c r="I7" s="57">
@@ -8280,11 +8321,11 @@
         </is>
       </c>
       <c r="B8" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A8,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$A8,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="C8" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$A8)-B8</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$A8)-B8</f>
         <v/>
       </c>
       <c r="D8" s="57">
@@ -8297,11 +8338,11 @@
         </is>
       </c>
       <c r="G8" s="40">
-        <f>COUNTIFS(準備リスト!$E$5:$E$119,$F8,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$E$5:$E$120,$F8,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="H8" s="40">
-        <f>COUNTIF(準備リスト!$E$5:$E$119,$F8)-G8</f>
+        <f>COUNTIF(準備リスト!$E$5:$E$120,$F8)-G8</f>
         <v/>
       </c>
       <c r="I8" s="57">
@@ -8316,11 +8357,11 @@
         </is>
       </c>
       <c r="B9" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A9,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$A9,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="C9" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$A9)-B9</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$A9)-B9</f>
         <v/>
       </c>
       <c r="D9" s="57">
@@ -8333,11 +8374,11 @@
         </is>
       </c>
       <c r="G9" s="40">
-        <f>COUNTIFS(準備リスト!$E$5:$E$119,$F9,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$E$5:$E$120,$F9,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="H9" s="40">
-        <f>COUNTIF(準備リスト!$E$5:$E$119,$F9)-G9</f>
+        <f>COUNTIF(準備リスト!$E$5:$E$120,$F9)-G9</f>
         <v/>
       </c>
       <c r="I9" s="57">
@@ -8352,11 +8393,11 @@
         </is>
       </c>
       <c r="B10" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A10,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$A10,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="C10" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$A10)-B10</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$A10)-B10</f>
         <v/>
       </c>
       <c r="D10" s="57">
@@ -8369,11 +8410,11 @@
         </is>
       </c>
       <c r="G10" s="40">
-        <f>COUNTIFS(準備リスト!$E$5:$E$119,$F10,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$E$5:$E$120,$F10,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="H10" s="40">
-        <f>COUNTIF(準備リスト!$E$5:$E$119,$F10)-G10</f>
+        <f>COUNTIF(準備リスト!$E$5:$E$120,$F10)-G10</f>
         <v/>
       </c>
       <c r="I10" s="57">
@@ -8388,11 +8429,11 @@
         </is>
       </c>
       <c r="B11" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A11,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$A11,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="C11" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$A11)-B11</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$A11)-B11</f>
         <v/>
       </c>
       <c r="D11" s="57">
@@ -8405,11 +8446,11 @@
         </is>
       </c>
       <c r="G11" s="40">
-        <f>COUNTIFS(準備リスト!$E$5:$E$119,$F11,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$E$5:$E$120,$F11,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="H11" s="40">
-        <f>COUNTIF(準備リスト!$E$5:$E$119,$F11)-G11</f>
+        <f>COUNTIF(準備リスト!$E$5:$E$120,$F11)-G11</f>
         <v/>
       </c>
       <c r="I11" s="57">
@@ -8424,11 +8465,11 @@
         </is>
       </c>
       <c r="B12" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A12,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$A12,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="C12" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$A12)-B12</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$A12)-B12</f>
         <v/>
       </c>
       <c r="D12" s="57">
@@ -8441,11 +8482,11 @@
         </is>
       </c>
       <c r="G12" s="40">
-        <f>COUNTIFS(準備リスト!$E$5:$E$119,$F12,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$E$5:$E$120,$F12,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="H12" s="40">
-        <f>COUNTIF(準備リスト!$E$5:$E$119,$F12)-G12</f>
+        <f>COUNTIF(準備リスト!$E$5:$E$120,$F12)-G12</f>
         <v/>
       </c>
       <c r="I12" s="57">
@@ -8460,11 +8501,11 @@
         </is>
       </c>
       <c r="B13" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A13,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$A13,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="C13" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$A13)-B13</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$A13)-B13</f>
         <v/>
       </c>
       <c r="D13" s="57">
@@ -8477,11 +8518,11 @@
         </is>
       </c>
       <c r="G13" s="40">
-        <f>COUNTIFS(準備リスト!$E$5:$E$119,$F13,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$E$5:$E$120,$F13,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="H13" s="40">
-        <f>COUNTIF(準備リスト!$E$5:$E$119,$F13)-G13</f>
+        <f>COUNTIF(準備リスト!$E$5:$E$120,$F13)-G13</f>
         <v/>
       </c>
       <c r="I13" s="57">
@@ -8496,11 +8537,11 @@
         </is>
       </c>
       <c r="B14" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A14,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$A14,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="C14" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$A14)-B14</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$A14)-B14</f>
         <v/>
       </c>
       <c r="D14" s="57">
@@ -8513,11 +8554,11 @@
         </is>
       </c>
       <c r="G14" s="40">
-        <f>COUNTIFS(準備リスト!$E$5:$E$119,$F14,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$E$5:$E$120,$F14,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="H14" s="40">
-        <f>COUNTIF(準備リスト!$E$5:$E$119,$F14)-G14</f>
+        <f>COUNTIF(準備リスト!$E$5:$E$120,$F14)-G14</f>
         <v/>
       </c>
       <c r="I14" s="57">
@@ -8532,11 +8573,11 @@
         </is>
       </c>
       <c r="B15" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A15,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$A15,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="C15" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$A15)-B15</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$A15)-B15</f>
         <v/>
       </c>
       <c r="D15" s="57">
@@ -8549,11 +8590,11 @@
         </is>
       </c>
       <c r="G15" s="40">
-        <f>COUNTIFS(準備リスト!$E$5:$E$119,$F15,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$E$5:$E$120,$F15,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="H15" s="40">
-        <f>COUNTIF(準備リスト!$E$5:$E$119,$F15)-G15</f>
+        <f>COUNTIF(準備リスト!$E$5:$E$120,$F15)-G15</f>
         <v/>
       </c>
       <c r="I15" s="57">
@@ -8568,11 +8609,11 @@
         </is>
       </c>
       <c r="B16" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A16,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$A16,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="C16" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$A16)-B16</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$A16)-B16</f>
         <v/>
       </c>
       <c r="D16" s="57">
@@ -8587,11 +8628,11 @@
         </is>
       </c>
       <c r="B17" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A17,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$A17,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="C17" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$A17)-B17</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$A17)-B17</f>
         <v/>
       </c>
       <c r="D17" s="57">
@@ -8623,11 +8664,11 @@
         </is>
       </c>
       <c r="B18" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A18,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$A18,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="C18" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$A18)-B18</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$A18)-B18</f>
         <v/>
       </c>
       <c r="D18" s="57">
@@ -8653,11 +8694,11 @@
         </is>
       </c>
       <c r="B19" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A19,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$A19,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="C19" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$A19)-B19</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$A19)-B19</f>
         <v/>
       </c>
       <c r="D19" s="57">
@@ -8672,11 +8713,11 @@
         </is>
       </c>
       <c r="B20" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A20,準備リスト!$I$5:$I$119,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$120,$A20,準備リスト!$I$5:$I$120,"完了")</f>
         <v/>
       </c>
       <c r="C20" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$119,$A20)-B20</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$120,$A20)-B20</f>
         <v/>
       </c>
       <c r="D20" s="57">
